--- a/src/test_data/data.xlsx
+++ b/src/test_data/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Personal\VSCODE\Playwright_Automation_TS\src\test_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{DEB6EB26-EFF7-462A-BBDF-537CF83EB987}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C7F751C-555C-4A34-AAA8-8CD0E64C9A49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{1120CC49-D95F-4BF2-BC9C-D733C0CBC652}"/>
   </bookViews>

--- a/src/test_data/data.xlsx
+++ b/src/test_data/data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Personal\VSCODE\Playwright_Automation_TS\src\test_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C7F751C-555C-4A34-AAA8-8CD0E64C9A49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78B018DA-2B80-442B-B340-39AFE7FE5898}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{1120CC49-D95F-4BF2-BC9C-D733C0CBC652}"/>
+    <workbookView xWindow="4248" yWindow="3276" windowWidth="17280" windowHeight="8964" xr2:uid="{1120CC49-D95F-4BF2-BC9C-D733C0CBC652}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -57,7 +57,7 @@
     <t>rahulshettyacademy</t>
   </si>
   <si>
-    <t>learning</t>
+    <t>Learning@830$3mK2</t>
   </si>
 </sst>
 </file>
@@ -427,7 +427,7 @@
     <col min="2" max="2" width="11.5546875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="44.44140625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="17.6640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.77734375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="18.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
@@ -473,6 +473,7 @@
   </sheetData>
   <hyperlinks>
     <hyperlink ref="D2" r:id="rId1" xr:uid="{88ABE6A8-C495-41D3-9932-0F9247A89139}"/>
+    <hyperlink ref="F2" r:id="rId2" xr:uid="{24EAAA17-E935-4786-BE1B-64E7EA3658A9}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
